--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,11 +489,7 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -531,11 +527,7 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -573,11 +565,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -615,11 +603,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -657,11 +641,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -699,11 +679,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -741,11 +717,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -783,11 +755,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -825,11 +793,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -867,11 +831,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -909,11 +869,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -951,11 +907,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -993,11 +945,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1035,11 +983,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1077,11 +1021,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1119,11 +1059,7 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -3559,6 +3495,678 @@
       <c r="H81" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>热线受理</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>在线技术支持</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>7×24</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1 小时</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2 小时</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>4 小时</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>技术咨询</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>8 小时</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>提供</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>软件更新授权</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3529,11 +3529,7 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3571,11 +3567,7 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3613,11 +3605,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3655,11 +3643,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3697,11 +3681,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3739,11 +3719,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3781,11 +3757,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3823,11 +3795,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3865,11 +3833,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3907,11 +3871,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3949,11 +3909,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -3991,11 +3947,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4033,11 +3985,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4075,11 +4023,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4117,11 +4061,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -4159,14 +4099,682 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>热线受理</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>在线技术支持</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7×24</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1 小时</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2 小时</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>4 小时</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>技术咨询</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>8 小时</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>提供</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>软件更新授权</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/维保SLA表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,7 +489,11 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -527,7 +531,11 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -565,7 +573,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -603,7 +615,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -641,7 +657,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -679,7 +699,11 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -717,7 +741,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -755,7 +783,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -793,7 +825,11 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -831,7 +867,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -869,7 +909,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -907,7 +951,11 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -945,7 +993,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -983,7 +1035,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1021,7 +1077,11 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -1059,7 +1119,11 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -4137,11 +4201,7 @@
           <t>热线受理</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4179,11 +4239,7 @@
           <t>在线技术支持</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4221,11 +4277,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4263,11 +4315,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4305,11 +4353,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4347,11 +4391,7 @@
           <t>远程问题处理（单域）</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4389,11 +4429,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4431,11 +4467,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4473,11 +4505,7 @@
           <t>现场问题处理</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4515,11 +4543,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4557,11 +4581,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4599,11 +4619,7 @@
           <t>备件先行</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4641,11 +4657,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4683,11 +4695,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4725,11 +4733,7 @@
           <t>现场硬件更换</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -4767,14 +4771,618 @@
           <t>软件更新授权</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>热线受理</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7×24×365</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>在线技术支持</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>7×24</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>1 小时</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2 小时</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4 小时</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>技术咨询</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>8 小时</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>远程问题处理（单域）</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>NBD人员到达</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>现场问题处理</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>NBD备件送达</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>备件先行</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>紧急问题</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>7×10</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>重要问题</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>一般问题</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5×8</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NBD完成更换</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>现场硬件更换</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>提供</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>软件更新授权</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
